--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/39.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/39.xlsx
@@ -426,13 +426,13 @@
         <v>-7.77755002809559</v>
       </c>
       <c r="E2">
-        <v>-16.75416491642391</v>
+        <v>-25.27873647047488</v>
       </c>
       <c r="F2">
-        <v>-2.959073474342832</v>
+        <v>-3.577589734623736</v>
       </c>
       <c r="G2">
-        <v>-11.92185498305325</v>
+        <v>-16.30408866902454</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.536189309236921</v>
       </c>
       <c r="E3">
-        <v>-16.73398603624573</v>
+        <v>-25.19618691778906</v>
       </c>
       <c r="F3">
-        <v>-2.656368972909628</v>
+        <v>-3.511679025485188</v>
       </c>
       <c r="G3">
-        <v>-10.6379426592854</v>
+        <v>-15.80662788829318</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.327865519486333</v>
       </c>
       <c r="E4">
-        <v>-18.31589069050117</v>
+        <v>-25.48234571880775</v>
       </c>
       <c r="F4">
-        <v>-3.214505533200476</v>
+        <v>-3.534416882324631</v>
       </c>
       <c r="G4">
-        <v>-10.47535183621518</v>
+        <v>-15.43080813758404</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.173198350131168</v>
       </c>
       <c r="E5">
-        <v>-18.71278879490344</v>
+        <v>-26.08820572781996</v>
       </c>
       <c r="F5">
-        <v>-3.012052539956277</v>
+        <v>-3.569308545697949</v>
       </c>
       <c r="G5">
-        <v>-10.34775679004059</v>
+        <v>-15.35561737202334</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.058092254444075</v>
       </c>
       <c r="E6">
-        <v>-18.17373283445238</v>
+        <v>-25.88878531794418</v>
       </c>
       <c r="F6">
-        <v>-2.953462113556268</v>
+        <v>-3.321914964117071</v>
       </c>
       <c r="G6">
-        <v>-9.622495715479213</v>
+        <v>-15.32605916617596</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.983245882159152</v>
       </c>
       <c r="E7">
-        <v>-19.2736357722794</v>
+        <v>-26.70863383771485</v>
       </c>
       <c r="F7">
-        <v>-2.817904758292546</v>
+        <v>-3.446695259470372</v>
       </c>
       <c r="G7">
-        <v>-9.936974367891199</v>
+        <v>-14.95096773548545</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.943260946602006</v>
       </c>
       <c r="E8">
-        <v>-19.04987481461239</v>
+        <v>-27.21242204259417</v>
       </c>
       <c r="F8">
-        <v>-2.67189837660991</v>
+        <v>-3.549183359646935</v>
       </c>
       <c r="G8">
-        <v>-10.36636536651683</v>
+        <v>-14.97990521404422</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.927144754993331</v>
       </c>
       <c r="E9">
-        <v>-20.89393735764588</v>
+        <v>-27.36797965323165</v>
       </c>
       <c r="F9">
-        <v>-2.780829518445448</v>
+        <v>-3.430503990215253</v>
       </c>
       <c r="G9">
-        <v>-9.600414376732273</v>
+        <v>-14.28465257952357</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.92000012664623</v>
       </c>
       <c r="E10">
-        <v>-18.90135445258283</v>
+        <v>-27.86966211769741</v>
       </c>
       <c r="F10">
-        <v>-3.150066832936703</v>
+        <v>-3.334521059252874</v>
       </c>
       <c r="G10">
-        <v>-8.444544022786816</v>
+        <v>-14.06420169679074</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.918420375920209</v>
       </c>
       <c r="E11">
-        <v>-21.14219283122038</v>
+        <v>-28.73420214744977</v>
       </c>
       <c r="F11">
-        <v>-3.271068116198432</v>
+        <v>-3.308285006871408</v>
       </c>
       <c r="G11">
-        <v>-9.768163029752683</v>
+        <v>-13.37924982471553</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.911516679636733</v>
       </c>
       <c r="E12">
-        <v>-21.92767476174683</v>
+        <v>-28.84074808390224</v>
       </c>
       <c r="F12">
-        <v>-2.266395965591496</v>
+        <v>-3.414707023843866</v>
       </c>
       <c r="G12">
-        <v>-9.119206719325971</v>
+        <v>-12.88687238665972</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.882864068157112</v>
       </c>
       <c r="E13">
-        <v>-22.4010859629827</v>
+        <v>-29.96997968363994</v>
       </c>
       <c r="F13">
-        <v>-2.316349005082515</v>
+        <v>-3.420329153406666</v>
       </c>
       <c r="G13">
-        <v>-7.764071318826242</v>
+        <v>-12.64556672230225</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.833334113409329</v>
       </c>
       <c r="E14">
-        <v>-22.86354731406802</v>
+        <v>-29.98456363418164</v>
       </c>
       <c r="F14">
-        <v>-2.827443408935782</v>
+        <v>-3.278210299945369</v>
       </c>
       <c r="G14">
-        <v>-9.139255383111797</v>
+        <v>-12.63159953067206</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.760073364907854</v>
       </c>
       <c r="E15">
-        <v>-23.36033902660549</v>
+        <v>-30.88033654916491</v>
       </c>
       <c r="F15">
-        <v>-2.376647525067097</v>
+        <v>-3.133192160574274</v>
       </c>
       <c r="G15">
-        <v>-8.077444249028114</v>
+        <v>-12.35810874258179</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.658939892000039</v>
       </c>
       <c r="E16">
-        <v>-24.37189596501687</v>
+        <v>-31.16455263483431</v>
       </c>
       <c r="F16">
-        <v>-2.20469336285917</v>
+        <v>-3.378349978534996</v>
       </c>
       <c r="G16">
-        <v>-7.795898903640795</v>
+        <v>-11.80372478657544</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.535784471105379</v>
       </c>
       <c r="E17">
-        <v>-24.8550252714732</v>
+        <v>-31.9090813106724</v>
       </c>
       <c r="F17">
-        <v>-2.302131735348267</v>
+        <v>-3.098828995603942</v>
       </c>
       <c r="G17">
-        <v>-6.929347056008866</v>
+        <v>-11.56493513682781</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.402204950082068</v>
       </c>
       <c r="E18">
-        <v>-24.63176244594703</v>
+        <v>-32.19885836242322</v>
       </c>
       <c r="F18">
-        <v>-1.440809392163189</v>
+        <v>-3.053156130483188</v>
       </c>
       <c r="G18">
-        <v>-6.524930812931498</v>
+        <v>-11.23649260333117</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.265321963069916</v>
       </c>
       <c r="E19">
-        <v>-23.95381365920672</v>
+        <v>-32.81639051319021</v>
       </c>
       <c r="F19">
-        <v>-2.062216654679863</v>
+        <v>-2.742684027913934</v>
       </c>
       <c r="G19">
-        <v>-6.857700229447959</v>
+        <v>-11.15164001061411</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.128162392314951</v>
       </c>
       <c r="E20">
-        <v>-27.28644900719755</v>
+        <v>-33.21630910975559</v>
       </c>
       <c r="F20">
-        <v>-1.379793506007783</v>
+        <v>-2.891313020793832</v>
       </c>
       <c r="G20">
-        <v>-5.997666845982854</v>
+        <v>-10.76180672063723</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.001197964884201</v>
       </c>
       <c r="E21">
-        <v>-26.9281108589706</v>
+        <v>-33.51599219839819</v>
       </c>
       <c r="F21">
-        <v>-1.425504476029065</v>
+        <v>-2.572563871135805</v>
       </c>
       <c r="G21">
-        <v>-5.70711019563764</v>
+        <v>-10.72061691303762</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.88440259818275</v>
       </c>
       <c r="E22">
-        <v>-27.72125496751803</v>
+        <v>-35.00074749976708</v>
       </c>
       <c r="F22">
-        <v>-1.46261450730708</v>
+        <v>-2.60488925229525</v>
       </c>
       <c r="G22">
-        <v>-5.317700655489788</v>
+        <v>-10.70966562839371</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.769131994323476</v>
       </c>
       <c r="E23">
-        <v>-26.69418347715637</v>
+        <v>-34.43799403483388</v>
       </c>
       <c r="F23">
-        <v>-1.140995892965755</v>
+        <v>-2.280120356721079</v>
       </c>
       <c r="G23">
-        <v>-5.103577880555267</v>
+        <v>-10.75520549283193</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.65626596980803</v>
       </c>
       <c r="E24">
-        <v>-29.55400764671736</v>
+        <v>-35.06079280087179</v>
       </c>
       <c r="F24">
-        <v>-1.200808161284894</v>
+        <v>-2.231670804066141</v>
       </c>
       <c r="G24">
-        <v>-6.470972231186916</v>
+        <v>-10.52313293998348</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.541685762558252</v>
       </c>
       <c r="E25">
-        <v>-29.39429063270383</v>
+        <v>-35.25894523802542</v>
       </c>
       <c r="F25">
-        <v>-1.129327509729921</v>
+        <v>-2.438250723711088</v>
       </c>
       <c r="G25">
-        <v>-5.130919676164108</v>
+        <v>-10.20734331153794</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.41729853822415</v>
       </c>
       <c r="E26">
-        <v>-28.3072530895326</v>
+        <v>-35.71803287597503</v>
       </c>
       <c r="F26">
-        <v>-0.9757846414166161</v>
+        <v>-2.332752336392751</v>
       </c>
       <c r="G26">
-        <v>-6.076113533081425</v>
+        <v>-10.88838211878573</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.280128998138019</v>
       </c>
       <c r="E27">
-        <v>-28.86838988924506</v>
+        <v>-35.11151850246871</v>
       </c>
       <c r="F27">
-        <v>-0.7236047529823627</v>
+        <v>-2.134371597300714</v>
       </c>
       <c r="G27">
-        <v>-5.073627375061481</v>
+        <v>-10.871544684173</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.13088290744558</v>
       </c>
       <c r="E28">
-        <v>-30.58807789365787</v>
+        <v>-35.93145985595653</v>
       </c>
       <c r="F28">
-        <v>-0.9950632359819691</v>
+        <v>-2.253695436571774</v>
       </c>
       <c r="G28">
-        <v>-4.857521583348936</v>
+        <v>-10.66789316477919</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.966332169134058</v>
       </c>
       <c r="E29">
-        <v>-28.94970316852678</v>
+        <v>-35.05243097361662</v>
       </c>
       <c r="F29">
-        <v>-0.8280295761466712</v>
+        <v>-2.208361373718766</v>
       </c>
       <c r="G29">
-        <v>-4.677858276932689</v>
+        <v>-11.09452316842507</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.782034071257885</v>
       </c>
       <c r="E30">
-        <v>-28.28615945760487</v>
+        <v>-35.07254645515869</v>
       </c>
       <c r="F30">
-        <v>-1.06524169397974</v>
+        <v>-2.219063052195533</v>
       </c>
       <c r="G30">
-        <v>-5.817255356274732</v>
+        <v>-10.63833661420458</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.584339274862083</v>
       </c>
       <c r="E31">
-        <v>-28.86402444030166</v>
+        <v>-34.97478575828111</v>
       </c>
       <c r="F31">
-        <v>-0.8100076149313651</v>
+        <v>-2.045366833339518</v>
       </c>
       <c r="G31">
-        <v>-6.198249489661756</v>
+        <v>-10.60967391092557</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.374745010033902</v>
       </c>
       <c r="E32">
-        <v>-27.46775099256865</v>
+        <v>-34.82874020729673</v>
       </c>
       <c r="F32">
-        <v>-0.3205543094762353</v>
+        <v>-2.109320938672654</v>
       </c>
       <c r="G32">
-        <v>-5.930797136635116</v>
+        <v>-11.2228465346183</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.152208154546177</v>
       </c>
       <c r="E33">
-        <v>-27.99698922137107</v>
+        <v>-33.77132794108368</v>
       </c>
       <c r="F33">
-        <v>-0.7772158629241439</v>
+        <v>-2.166340780476955</v>
       </c>
       <c r="G33">
-        <v>-6.0833106590838</v>
+        <v>-11.27563649378751</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.92443938969193</v>
       </c>
       <c r="E34">
-        <v>-28.5115280235446</v>
+        <v>-34.322936831484</v>
       </c>
       <c r="F34">
-        <v>-0.7899636088858255</v>
+        <v>-2.149605273838197</v>
       </c>
       <c r="G34">
-        <v>-5.184490924080595</v>
+        <v>-11.16652753390422</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.697137731986968</v>
       </c>
       <c r="E35">
-        <v>-26.95741008580023</v>
+        <v>-33.53944290104692</v>
       </c>
       <c r="F35">
-        <v>-0.7754431566821529</v>
+        <v>-2.077198507526895</v>
       </c>
       <c r="G35">
-        <v>-6.992234179072861</v>
+        <v>-11.31849481633892</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.47265063412716</v>
       </c>
       <c r="E36">
-        <v>-28.34803199797167</v>
+        <v>-33.17188704397735</v>
       </c>
       <c r="F36">
-        <v>-1.212103779189468</v>
+        <v>-2.102574714544255</v>
       </c>
       <c r="G36">
-        <v>-4.953073859248921</v>
+        <v>-11.24208742529254</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.255215106655674</v>
       </c>
       <c r="E37">
-        <v>-26.199221268118</v>
+        <v>-32.6595196450905</v>
       </c>
       <c r="F37">
-        <v>-0.7090114044472438</v>
+        <v>-2.119169398724537</v>
       </c>
       <c r="G37">
-        <v>-6.424733841639916</v>
+        <v>-11.21656974027584</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.051261161265621</v>
       </c>
       <c r="E38">
-        <v>-27.21542894933526</v>
+        <v>-32.29389291794819</v>
       </c>
       <c r="F38">
-        <v>-0.6313221392082894</v>
+        <v>-2.066489373743503</v>
       </c>
       <c r="G38">
-        <v>-5.607257521082142</v>
+        <v>-11.5221099197318</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.862363703767804</v>
       </c>
       <c r="E39">
-        <v>-24.98589364182086</v>
+        <v>-31.97376376916096</v>
       </c>
       <c r="F39">
-        <v>-0.5912979114072257</v>
+        <v>-2.069116955145183</v>
       </c>
       <c r="G39">
-        <v>-6.062136409814621</v>
+        <v>-11.49001418072856</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.686603325744787</v>
       </c>
       <c r="E40">
-        <v>-25.23579747993415</v>
+        <v>-31.59797061787144</v>
       </c>
       <c r="F40">
-        <v>-0.5637555236315449</v>
+        <v>-1.966508741695214</v>
       </c>
       <c r="G40">
-        <v>-5.50483917373371</v>
+        <v>-11.24571909374912</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.52926255997503</v>
       </c>
       <c r="E41">
-        <v>-24.00484956127316</v>
+        <v>-31.40584331538501</v>
       </c>
       <c r="F41">
-        <v>-0.8521748292034712</v>
+        <v>-1.908121265308891</v>
       </c>
       <c r="G41">
-        <v>-5.426875826283873</v>
+        <v>-11.63129171161696</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.390387633686612</v>
       </c>
       <c r="E42">
-        <v>-24.9241071424602</v>
+        <v>-31.32232466926155</v>
       </c>
       <c r="F42">
-        <v>-0.2564635235216375</v>
+        <v>-2.098345070585561</v>
       </c>
       <c r="G42">
-        <v>-6.411485038391753</v>
+        <v>-11.96385256376445</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.267421193510758</v>
       </c>
       <c r="E43">
-        <v>-22.77050528710642</v>
+        <v>-30.67636049443741</v>
       </c>
       <c r="F43">
-        <v>-0.7271335981182886</v>
+        <v>-1.901258241376697</v>
       </c>
       <c r="G43">
-        <v>-6.364432254642091</v>
+        <v>-11.36986124092625</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.162110524608424</v>
       </c>
       <c r="E44">
-        <v>-23.54046360873458</v>
+        <v>-29.79150120181263</v>
       </c>
       <c r="F44">
-        <v>-0.6468117812732374</v>
+        <v>-2.089890752872589</v>
       </c>
       <c r="G44">
-        <v>-6.301972191952662</v>
+        <v>-11.68026130123386</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.075345584151083</v>
       </c>
       <c r="E45">
-        <v>-22.74276838380944</v>
+        <v>-29.33549745466225</v>
       </c>
       <c r="F45">
-        <v>-0.6713604492552007</v>
+        <v>-1.706055948009201</v>
       </c>
       <c r="G45">
-        <v>-5.819907103251688</v>
+        <v>-11.73227990329243</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.004971509540493</v>
       </c>
       <c r="E46">
-        <v>-21.41280085249673</v>
+        <v>-29.49463482400279</v>
       </c>
       <c r="F46">
-        <v>-0.6095012850837448</v>
+        <v>-1.763147857777546</v>
       </c>
       <c r="G46">
-        <v>-5.707219443640436</v>
+        <v>-11.82705420099068</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.948140823712123</v>
       </c>
       <c r="E47">
-        <v>-21.26780817171914</v>
+        <v>-28.7114918503013</v>
       </c>
       <c r="F47">
-        <v>-0.8784307624026043</v>
+        <v>-1.697247917415234</v>
       </c>
       <c r="G47">
-        <v>-6.265572743748375</v>
+        <v>-12.02260812599543</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.906095617246258</v>
       </c>
       <c r="E48">
-        <v>-20.91218257942278</v>
+        <v>-28.14566807999091</v>
       </c>
       <c r="F48">
-        <v>-0.3885566463068523</v>
+        <v>-1.802955053319077</v>
       </c>
       <c r="G48">
-        <v>-6.329161702466696</v>
+        <v>-12.39272380674041</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.877177516249317</v>
       </c>
       <c r="E49">
-        <v>-20.9046924834141</v>
+        <v>-28.00835569113033</v>
       </c>
       <c r="F49">
-        <v>-0.6413901166219146</v>
+        <v>-1.715245027608457</v>
       </c>
       <c r="G49">
-        <v>-6.16571013755626</v>
+        <v>-12.2235085820461</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.857347873952945</v>
       </c>
       <c r="E50">
-        <v>-21.33259252087288</v>
+        <v>-27.23264620751242</v>
       </c>
       <c r="F50">
-        <v>-0.6767779720695094</v>
+        <v>-1.801428372195717</v>
       </c>
       <c r="G50">
-        <v>-6.811183754075659</v>
+        <v>-12.20749547327265</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.848868644723178</v>
       </c>
       <c r="E51">
-        <v>-21.2806554524789</v>
+        <v>-26.41152065807159</v>
       </c>
       <c r="F51">
-        <v>-0.0873813110992164</v>
+        <v>-1.712288584347865</v>
       </c>
       <c r="G51">
-        <v>-7.229054054224626</v>
+        <v>-12.46413558456803</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.852964934199286</v>
       </c>
       <c r="E52">
-        <v>-19.97207590390443</v>
+        <v>-26.43703408063081</v>
       </c>
       <c r="F52">
-        <v>0.0905462084502978</v>
+        <v>-1.662174841580703</v>
       </c>
       <c r="G52">
-        <v>-6.604933456433526</v>
+        <v>-12.93261419437583</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.870209927175816</v>
       </c>
       <c r="E53">
-        <v>-17.68119335900811</v>
+        <v>-25.63506850471644</v>
       </c>
       <c r="F53">
-        <v>-0.01736521311239379</v>
+        <v>-1.838844071045365</v>
       </c>
       <c r="G53">
-        <v>-7.546949189633142</v>
+        <v>-12.72806882768642</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.903764068755439</v>
       </c>
       <c r="E54">
-        <v>-19.47910169495542</v>
+        <v>-25.32520767074159</v>
       </c>
       <c r="F54">
-        <v>-0.283986030479651</v>
+        <v>-1.603691274575656</v>
       </c>
       <c r="G54">
-        <v>-7.336650094796479</v>
+        <v>-12.52236477005827</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.959466633332122</v>
       </c>
       <c r="E55">
-        <v>-18.74552966197889</v>
+        <v>-25.04087837322199</v>
       </c>
       <c r="F55">
-        <v>-1.0402854692356</v>
+        <v>-2.191965497715155</v>
       </c>
       <c r="G55">
-        <v>-7.078950608928531</v>
+        <v>-12.72761528294754</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.040769118657933</v>
       </c>
       <c r="E56">
-        <v>-17.51379831731458</v>
+        <v>-24.87187572325574</v>
       </c>
       <c r="F56">
-        <v>-0.1512277286699883</v>
+        <v>-1.653390833641417</v>
       </c>
       <c r="G56">
-        <v>-7.065523036221247</v>
+        <v>-12.88802445650739</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.14688562007477</v>
       </c>
       <c r="E57">
-        <v>-19.20846197436101</v>
+        <v>-25.15581557201067</v>
       </c>
       <c r="F57">
-        <v>-0.4431452297839369</v>
+        <v>-2.030618580100076</v>
       </c>
       <c r="G57">
-        <v>-7.921603628312462</v>
+        <v>-12.66905173235784</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.282412329913724</v>
       </c>
       <c r="E58">
-        <v>-16.85878625142312</v>
+        <v>-24.35989098042253</v>
       </c>
       <c r="F58">
-        <v>-0.553587313762181</v>
+        <v>-1.802139939794722</v>
       </c>
       <c r="G58">
-        <v>-7.881754591656255</v>
+        <v>-12.8055124194866</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.447035351473975</v>
       </c>
       <c r="E59">
-        <v>-18.06117308451773</v>
+        <v>-24.34388282480542</v>
       </c>
       <c r="F59">
-        <v>-0.5287793667831414</v>
+        <v>-1.835273807539299</v>
       </c>
       <c r="G59">
-        <v>-7.768421375664845</v>
+        <v>-13.35467564517752</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.63490977197837</v>
       </c>
       <c r="E60">
-        <v>-17.12570809485723</v>
+        <v>-24.2415574261281</v>
       </c>
       <c r="F60">
-        <v>-0.4451714164511845</v>
+        <v>-1.931178871965815</v>
       </c>
       <c r="G60">
-        <v>-7.637333703946323</v>
+        <v>-13.24347110996786</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.842395598141753</v>
       </c>
       <c r="E61">
-        <v>-17.08338497678154</v>
+        <v>-24.10113397562425</v>
       </c>
       <c r="F61">
-        <v>-0.6808841892851866</v>
+        <v>-1.625892349338085</v>
       </c>
       <c r="G61">
-        <v>-7.436072398431871</v>
+        <v>-13.2130339542798</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.064740871221229</v>
       </c>
       <c r="E62">
-        <v>-15.35623404720408</v>
+        <v>-23.66882773295601</v>
       </c>
       <c r="F62">
-        <v>-0.6390715162614787</v>
+        <v>-1.911544079417258</v>
       </c>
       <c r="G62">
-        <v>-7.910500058573747</v>
+        <v>-13.85149086952871</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.293059387544822</v>
       </c>
       <c r="E63">
-        <v>-18.03315088735826</v>
+        <v>-24.18856069481633</v>
       </c>
       <c r="F63">
-        <v>-0.6605370007702224</v>
+        <v>-1.660839513327391</v>
       </c>
       <c r="G63">
-        <v>-6.858743051292829</v>
+        <v>-13.31214837718004</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.517237144468369</v>
       </c>
       <c r="E64">
-        <v>-15.92559908418848</v>
+        <v>-24.09352613929136</v>
       </c>
       <c r="F64">
-        <v>-0.8820581832594633</v>
+        <v>-1.973478625022369</v>
       </c>
       <c r="G64">
-        <v>-8.351441550585893</v>
+        <v>-13.46099712571675</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.731049764005104</v>
       </c>
       <c r="E65">
-        <v>-15.26470000208704</v>
+        <v>-23.17277869015579</v>
       </c>
       <c r="F65">
-        <v>-0.5961587713268531</v>
+        <v>-1.849007310710312</v>
       </c>
       <c r="G65">
-        <v>-7.998348695003846</v>
+        <v>-13.21796335658777</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.925822383276747</v>
       </c>
       <c r="E66">
-        <v>-17.43000343427665</v>
+        <v>-22.97881056298525</v>
       </c>
       <c r="F66">
-        <v>-0.6565583521345763</v>
+        <v>-1.846024359692831</v>
       </c>
       <c r="G66">
-        <v>-8.264705257456988</v>
+        <v>-13.33415688392511</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.090499228864737</v>
       </c>
       <c r="E67">
-        <v>-15.45966439353927</v>
+        <v>-23.73891492517272</v>
       </c>
       <c r="F67">
-        <v>-1.097210048788579</v>
+        <v>-1.905827515970539</v>
       </c>
       <c r="G67">
-        <v>-7.961250721690774</v>
+        <v>-13.12947247432306</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.222290615082367</v>
       </c>
       <c r="E68">
-        <v>-16.65499133565593</v>
+        <v>-22.67427521444343</v>
       </c>
       <c r="F68">
-        <v>-0.5931749919419693</v>
+        <v>-1.923516473489919</v>
       </c>
       <c r="G68">
-        <v>-7.850671879588037</v>
+        <v>-13.30366013841735</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.317530237628681</v>
       </c>
       <c r="E69">
-        <v>-15.38489928767264</v>
+        <v>-23.15135447962551</v>
       </c>
       <c r="F69">
-        <v>-0.3146190570351768</v>
+        <v>-1.845424621693204</v>
       </c>
       <c r="G69">
-        <v>-7.779703714862681</v>
+        <v>-13.735666468019</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.371552472180881</v>
       </c>
       <c r="E70">
-        <v>-16.07027024331152</v>
+        <v>-22.8686146764826</v>
       </c>
       <c r="F70">
-        <v>-1.074273383772463</v>
+        <v>-2.013584032828907</v>
       </c>
       <c r="G70">
-        <v>-9.298856783560062</v>
+        <v>-13.26448976359669</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.385114356253131</v>
       </c>
       <c r="E71">
-        <v>-14.76298583830324</v>
+        <v>-23.01690861481178</v>
       </c>
       <c r="F71">
-        <v>-1.031482408846049</v>
+        <v>-1.794546295813259</v>
       </c>
       <c r="G71">
-        <v>-7.661490754746385</v>
+        <v>-13.27970172034964</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.360805819526662</v>
       </c>
       <c r="E72">
-        <v>-16.66355468000443</v>
+        <v>-23.30208926544482</v>
       </c>
       <c r="F72">
-        <v>-0.7581087404111705</v>
+        <v>-2.055106777261635</v>
       </c>
       <c r="G72">
-        <v>-7.479616003909905</v>
+        <v>-13.34442619618793</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.299429913420733</v>
       </c>
       <c r="E73">
-        <v>-15.99005285473965</v>
+        <v>-22.86380090861245</v>
       </c>
       <c r="F73">
-        <v>-0.8616894571920263</v>
+        <v>-2.343573299775521</v>
       </c>
       <c r="G73">
-        <v>-7.90448810787443</v>
+        <v>-13.28299902370676</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.202121047920922</v>
       </c>
       <c r="E74">
-        <v>-15.02873480696936</v>
+        <v>-23.58946622597158</v>
       </c>
       <c r="F74">
-        <v>-0.9092543134607739</v>
+        <v>-2.265636352683129</v>
       </c>
       <c r="G74">
-        <v>-8.571096247116536</v>
+        <v>-12.6608548216026</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.073131974950673</v>
       </c>
       <c r="E75">
-        <v>-16.17518592912123</v>
+        <v>-23.66234748665103</v>
       </c>
       <c r="F75">
-        <v>-1.213621348271396</v>
+        <v>-2.066036256774172</v>
       </c>
       <c r="G75">
-        <v>-7.453055497048332</v>
+        <v>-12.932332798005</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.91315432450749</v>
       </c>
       <c r="E76">
-        <v>-18.16300487952821</v>
+        <v>-24.29365299111234</v>
       </c>
       <c r="F76">
-        <v>-0.7554786739072821</v>
+        <v>-2.200824887088096</v>
       </c>
       <c r="G76">
-        <v>-8.15191166038848</v>
+        <v>-12.78494731059664</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.720588274380005</v>
       </c>
       <c r="E77">
-        <v>-18.66814256966181</v>
+        <v>-23.40683286924224</v>
       </c>
       <c r="F77">
-        <v>-1.419920451366794</v>
+        <v>-2.340214269957169</v>
       </c>
       <c r="G77">
-        <v>-8.503279721744567</v>
+        <v>-12.68785232047536</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.500444702944443</v>
       </c>
       <c r="E78">
-        <v>-18.60672287669578</v>
+        <v>-24.62818042300696</v>
       </c>
       <c r="F78">
-        <v>-1.530231653295395</v>
+        <v>-2.37678751915817</v>
       </c>
       <c r="G78">
-        <v>-6.470737182453629</v>
+        <v>-12.53201501030524</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.254385213792235</v>
       </c>
       <c r="E79">
-        <v>-17.74670226400307</v>
+        <v>-24.78588905879809</v>
       </c>
       <c r="F79">
-        <v>-1.577214167279975</v>
+        <v>-2.459782477612055</v>
       </c>
       <c r="G79">
-        <v>-7.597047675278932</v>
+        <v>-12.52627783488569</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.982610012558442</v>
       </c>
       <c r="E80">
-        <v>-17.51008496862829</v>
+        <v>-25.44451031847367</v>
       </c>
       <c r="F80">
-        <v>-1.667800284613115</v>
+        <v>-2.445922234228413</v>
       </c>
       <c r="G80">
-        <v>-6.875567243723405</v>
+        <v>-12.51310186363939</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.690023374828138</v>
       </c>
       <c r="E81">
-        <v>-18.96209940292172</v>
+        <v>-25.320724481474</v>
       </c>
       <c r="F81">
-        <v>-1.622649290956125</v>
+        <v>-2.48976440738898</v>
       </c>
       <c r="G81">
-        <v>-6.870270370860572</v>
+        <v>-12.58956884450548</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.380960771705521</v>
       </c>
       <c r="E82">
-        <v>-19.88974824644498</v>
+        <v>-26.01839024404371</v>
       </c>
       <c r="F82">
-        <v>-1.198707421551394</v>
+        <v>-2.766121855208743</v>
       </c>
       <c r="G82">
-        <v>-6.469767192610622</v>
+        <v>-12.0983997555715</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.059040579982047</v>
       </c>
       <c r="E83">
-        <v>-20.00355332673174</v>
+        <v>-26.55328000840771</v>
       </c>
       <c r="F83">
-        <v>-1.561345961311948</v>
+        <v>-2.8175361347983</v>
       </c>
       <c r="G83">
-        <v>-6.237966104496393</v>
+        <v>-12.03396991828621</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.730965989867052</v>
       </c>
       <c r="E84">
-        <v>-20.91400302597387</v>
+        <v>-27.87446230014553</v>
       </c>
       <c r="F84">
-        <v>-2.008753822503183</v>
+        <v>-2.900072177711034</v>
       </c>
       <c r="G84">
-        <v>-6.621370315036007</v>
+        <v>-12.08201917624319</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.408265905328103</v>
       </c>
       <c r="E85">
-        <v>-21.17368836794372</v>
+        <v>-27.50094470704487</v>
       </c>
       <c r="F85">
-        <v>-1.186266171528748</v>
+        <v>-2.755025045480841</v>
       </c>
       <c r="G85">
-        <v>-5.72736742379244</v>
+        <v>-11.57473766216959</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.101397418913553</v>
       </c>
       <c r="E86">
-        <v>-22.11358673365773</v>
+        <v>-28.98204552988957</v>
       </c>
       <c r="F86">
-        <v>-1.521812127013341</v>
+        <v>-2.846581181042659</v>
       </c>
       <c r="G86">
-        <v>-6.024958983408606</v>
+        <v>-11.68599516610788</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.8193631471966012</v>
       </c>
       <c r="E87">
-        <v>-25.3670688844685</v>
+        <v>-29.43425215158452</v>
       </c>
       <c r="F87">
-        <v>-2.414248778214972</v>
+        <v>-2.970482578581589</v>
       </c>
       <c r="G87">
-        <v>-4.818914001269955</v>
+        <v>-11.75405005075867</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.5769204927233361</v>
       </c>
       <c r="E88">
-        <v>-25.26686281162677</v>
+        <v>-30.14486708557916</v>
       </c>
       <c r="F88">
-        <v>-2.237152939537868</v>
+        <v>-2.826557884182189</v>
       </c>
       <c r="G88">
-        <v>-5.459517805301087</v>
+        <v>-11.64264026172558</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.3864715805704622</v>
       </c>
       <c r="E89">
-        <v>-27.18533723955429</v>
+        <v>-31.19022228974679</v>
       </c>
       <c r="F89">
-        <v>-1.737825494641368</v>
+        <v>-3.149562357188397</v>
       </c>
       <c r="G89">
-        <v>-5.298843788098099</v>
+        <v>-11.72459281655024</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.258381407407902</v>
       </c>
       <c r="E90">
-        <v>-27.95830699639755</v>
+        <v>-32.70328055366362</v>
       </c>
       <c r="F90">
-        <v>-1.654104057975228</v>
+        <v>-3.363551194883983</v>
       </c>
       <c r="G90">
-        <v>-5.126344502228835</v>
+        <v>-11.61042534308293</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.2036540889763699</v>
       </c>
       <c r="E91">
-        <v>-27.84796619872666</v>
+        <v>-33.15984809582795</v>
       </c>
       <c r="F91">
-        <v>-1.649830510544185</v>
+        <v>-3.510731373176385</v>
       </c>
       <c r="G91">
-        <v>-5.004807754391111</v>
+        <v>-11.41880434617884</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.2339885652311351</v>
       </c>
       <c r="E92">
-        <v>-30.53306146293869</v>
+        <v>-34.51155230237748</v>
       </c>
       <c r="F92">
-        <v>-2.088956354442231</v>
+        <v>-3.29281607399153</v>
       </c>
       <c r="G92">
-        <v>-5.421264451594809</v>
+        <v>-11.98487121739328</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.3558335443513215</v>
       </c>
       <c r="E93">
-        <v>-31.75575397348369</v>
+        <v>-35.999042802047</v>
       </c>
       <c r="F93">
-        <v>-2.767809239608245</v>
+        <v>-3.538339201976887</v>
       </c>
       <c r="G93">
-        <v>-5.791956167263622</v>
+        <v>-11.73647105394514</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.5677338894412309</v>
       </c>
       <c r="E94">
-        <v>-32.85299416859421</v>
+        <v>-37.94330915368521</v>
       </c>
       <c r="F94">
-        <v>-2.163976619909366</v>
+        <v>-3.513957035842886</v>
       </c>
       <c r="G94">
-        <v>-6.2044997996399</v>
+        <v>-11.68247936674517</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.869725323112765</v>
       </c>
       <c r="E95">
-        <v>-33.89991396053149</v>
+        <v>-39.26738740455095</v>
       </c>
       <c r="F95">
-        <v>-2.345997931163515</v>
+        <v>-3.677315229511963</v>
       </c>
       <c r="G95">
-        <v>-5.931909479936311</v>
+        <v>-12.28407832323261</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.260385104684184</v>
       </c>
       <c r="E96">
-        <v>-35.94666873591129</v>
+        <v>-40.74034603112985</v>
       </c>
       <c r="F96">
-        <v>-2.798467945553258</v>
+        <v>-3.660298077956253</v>
       </c>
       <c r="G96">
-        <v>-5.572682183469994</v>
+        <v>-11.90885116017499</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.720635530969009</v>
       </c>
       <c r="E97">
-        <v>-38.73586682484865</v>
+        <v>-42.16624249158404</v>
       </c>
       <c r="F97">
-        <v>-2.443389915078055</v>
+        <v>-3.89890350976083</v>
       </c>
       <c r="G97">
-        <v>-5.601298539111454</v>
+        <v>-12.22756731087725</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.251556552876639</v>
       </c>
       <c r="E98">
-        <v>-39.90046807082326</v>
+        <v>-43.74216956014936</v>
       </c>
       <c r="F98">
-        <v>-2.948057844620404</v>
+        <v>-4.175760463124481</v>
       </c>
       <c r="G98">
-        <v>-7.000076861455395</v>
+        <v>-12.52131863766786</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.820520541199122</v>
       </c>
       <c r="E99">
-        <v>-41.8540200584142</v>
+        <v>-45.33156657465049</v>
       </c>
       <c r="F99">
-        <v>-3.15347473643182</v>
+        <v>-3.955648333587402</v>
       </c>
       <c r="G99">
-        <v>-5.156976980103711</v>
+        <v>-12.70101836008504</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.442574011602458</v>
       </c>
       <c r="E100">
-        <v>-43.62093778249002</v>
+        <v>-47.27162370969857</v>
       </c>
       <c r="F100">
-        <v>-2.678128527846365</v>
+        <v>-4.27342995011896</v>
       </c>
       <c r="G100">
-        <v>-6.636449849967387</v>
+        <v>-12.48417762726278</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.049002567916142</v>
       </c>
       <c r="E101">
-        <v>-46.65153070688025</v>
+        <v>-48.72417703239891</v>
       </c>
       <c r="F101">
-        <v>-3.601305064998483</v>
+        <v>-4.529146967363167</v>
       </c>
       <c r="G101">
-        <v>-7.29262977076079</v>
+        <v>-13.12061014391443</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.711491793761892</v>
       </c>
       <c r="E102">
-        <v>-48.69263734305399</v>
+        <v>-51.14460336899565</v>
       </c>
       <c r="F102">
-        <v>-3.289542366015667</v>
+        <v>-4.70449992102478</v>
       </c>
       <c r="G102">
-        <v>-6.536799118689785</v>
+        <v>-13.43836292586475</v>
       </c>
     </row>
   </sheetData>
